--- a/naver-place-crawler/results_nail/해운대구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/해운대구_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V170"/>
+  <dimension ref="A1:V239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16218,6 +16218,6412 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>네일혜주</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>parcom0228@naver.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0507-1434-8400</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로 95 센텀대림아파트 110동쪽 (대림상가 지하)</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_hyeju</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>7</v>
+      </c>
+      <c r="R171" t="n">
+        <v>235</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>1137379337</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137379337</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ZOONAIL 해운대점</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0507-1412-3107</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 양운로 53 투모로우 오피스텔 상가2층 204호</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zoonail_/</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>687</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>237</v>
+      </c>
+      <c r="R172" t="n">
+        <v>924</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>466729990</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/466729990</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>플라워바이허니팟</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>051-323-4182</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로157번길 16 1층 앤뷰티</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>http://flowerbyhoneypot.com/</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>35877879</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35877879</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>네일비기닝</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>wjdgml2851@naver.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0507-1316-0140</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 양운로42번길 11 201호</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_beginning__</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>25</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>1487470419</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487470419</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>morningapple6@naver.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0507-1349-1441</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 좌동순환로433번길 30-1 2층 217호</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>13</v>
+      </c>
+      <c r="R175" t="n">
+        <v>15</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>1525952926</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1525952926</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>케어네일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>loosetime@naver.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0507-1398-4231</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로483번길 10 상가동 3층 301-1호 (롯데아파트 상가)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/care_nail_busan</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>13</v>
+      </c>
+      <c r="R176" t="n">
+        <v>126</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>1263555849</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1263555849</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>네일모해</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>nec1153@naver.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 송정중앙로36번길 5-1 2층</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>http://instagram.com/hwang_josin_gram</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R177" t="n">
+        <v>5</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>1955718056</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1955718056</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>디어 모먼트네일</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sweetdreama@naver.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0507-1366-5839</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 청사포로 27 상가동 206호</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_ixfxknG</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>1135615215</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1135615215</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>아베크 네일</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>avecbeaute_@naver.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티3로 46 우신골든메르시아 지하상가1층 103호</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>1391888149</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391888149</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>시리뷰티</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>siribeauty24@naver.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 대천로103번길 29 222호</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>1721611007</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1721611007</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>엠앤드네일</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>tjddms7721@naver.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 재송1로 64 1층 m,and nail(엠앤드네일)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_SDVxgb</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>5</v>
+      </c>
+      <c r="R181" t="n">
+        <v>15</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>1683292765</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1683292765</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>네일온딘</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>leeinhee123@naver.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0507-1322-7480</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 양운로42번길 16 405호</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2014140688</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2014140688</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>묭띠끄뷰티</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>dbswjd3206@naver.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0507-1409-0423</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 재반로226번길 24 1층</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xlxnxoKb</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>10</v>
+      </c>
+      <c r="R183" t="n">
+        <v>367</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>1017000054</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1017000054</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>포쉬네일 반여점</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>eaippy@naver.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0507-1375-4177</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로21번길 37 홈플러스 반여점 2층</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/eaippy</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>660</v>
+      </c>
+      <c r="R184" t="n">
+        <v>940</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>32455942</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32455942</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>여우숲네일</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>hanna7342@naver.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로483번길 3</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>37973848</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37973848</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>올리네일</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>alsdk5109@naver.com</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>051-728-4144</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로 95 센텀 대림아파트 상가 12동 201호</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ollinailyoon</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>2</v>
+      </c>
+      <c r="R186" t="n">
+        <v>86</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>1185190104</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185190104</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>네일테일</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>suejinism@naver.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0507-1439-8869</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀동로 9 트럼프월드센텀 107호</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailtail_official</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>822</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>244</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1066</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>1159189090</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1159189090</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>손리사 네일</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>miracle9707@naver.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0507-1351-5204</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 814 세종월드프라자 A동 2층 손리사뷰티</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sonrisa_nail315?igsh=ZW1oM2IwNjZscHU0</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>3</v>
+      </c>
+      <c r="R188" t="n">
+        <v>137</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>1097644605</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1097644605</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>오르다뷰티왁싱네일</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>eb0o0@naver.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>0507-1350-0572</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 790 217호 오르다뷰티</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/o.rda_beauty_nail</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>578</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>24</v>
+      </c>
+      <c r="R189" t="n">
+        <v>602</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>1967337555</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1967337555</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>썬뷰티네일</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>artst_snu@naver.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0507-1362-7612</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로 81-1 2층</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>8</v>
+      </c>
+      <c r="R190" t="n">
+        <v>14</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>1893144350</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893144350</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>eienn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0507-1306-6785</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로21번길 21 1층 41호</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nailstudio41</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>1338366768</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338366768</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>예뻐지니</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>130727ya@naver.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 284 상가동 2층 204호</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/splgVr6c</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>3</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>1501870755</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501870755</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>morningapple6@naver.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 반여로27번길 9 1층 제이네일</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>http://instagram.com/j_nail_1112</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>8</v>
+      </c>
+      <c r="R193" t="n">
+        <v>19</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>76777862</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/76777862</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1프로네일</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>eunji-1009@naver.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0507-1353-4941</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 789 파밀리에펄시티 109호</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onebeauty_eunji</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>20</v>
+      </c>
+      <c r="R194" t="n">
+        <v>29</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>34975315</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34975315</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>풋토리&amp;네일테라스 센텀점</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>dana2348@naver.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0507-1491-2441</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀동로 26 A동 101호</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xmXYqxb</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>59</v>
+      </c>
+      <c r="R195" t="n">
+        <v>229</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>32800354</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32800354</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>클레오네일</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>blab27@naver.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0507-1400-4414</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀동로 25 대우월드마크센텀상가129호</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s3kg2W0b</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>148</v>
+      </c>
+      <c r="R196" t="n">
+        <v>412</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>37779025</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37779025</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>코스모젤네일</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>duduliz@naver.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0507-1445-4490</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 814 세종월드프라자 403호</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cosmogelnail</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>27</v>
+      </c>
+      <c r="R197" t="n">
+        <v>27</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>21593237</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21593237</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tiffany Nail</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>crossroads08@naver.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>051-552-0702</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 701-14호 티파니뷰티</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>12</v>
+      </c>
+      <c r="R198" t="n">
+        <v>12</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>21052308</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21052308</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>바비네일</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>zasd43@naver.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0507-1335-9685</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 7층 701-21 일부호</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/idagyo667</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>2050167285</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2050167285</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>네일핏</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>nailfitsl@naver.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0507-1382-0352</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 7층 7-11호</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__fit</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>6</v>
+      </c>
+      <c r="R200" t="n">
+        <v>54</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>1459693385</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1459693385</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>오션네일뷰티샵</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ocean_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0507-1391-8377</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대해변로 203 오션타워 5층 520호</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>1004784775</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004784775</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>리밸리네일</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sazlsazl@naver.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0507-1305-1624</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 7층 701-5호</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/livalley_nail</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>3</v>
+      </c>
+      <c r="R202" t="n">
+        <v>54</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>2077636087</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2077636087</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>네일시즈닝</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>blue991013@naver.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0507-1394-4788</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 대천로103번길 61 엘지상가 205호</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailseasoning</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>4</v>
+      </c>
+      <c r="R203" t="n">
+        <v>7</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>1667282471</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1667282471</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>채은네일</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sonbit_chae_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 43 5층 503호</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/c_e_nail/?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>622</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>1470560962</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470560962</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>더반하다네일</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>babyeun12@naver.com</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0507-1415-4249</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티3로 46 B동 지하1층 102-1호</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the.banhada.nail</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>3</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>2043562703</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2043562703</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>호감네일</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>skyseashell@naver.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>0507-1401-7807</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 48 상가 112호</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hogam_nail</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>15</v>
+      </c>
+      <c r="R206" t="n">
+        <v>38</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>1946368844</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1946368844</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>살롱드제이 뷰티</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>pks9158@naver.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>051-744-5558</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 158 동부아파트상가 지하1층</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/salon_de_j_beauty</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>5</v>
+      </c>
+      <c r="R207" t="n">
+        <v>31</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>1010249666</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010249666</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>정채민네일 마린점</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>jcmnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>0507-1300-9653</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티2로 2 마린파크 204호</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jcmnail</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>497</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>89</v>
+      </c>
+      <c r="R208" t="n">
+        <v>586</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>1275388458</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1275388458</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>네일피어나 속눈썹 왁싱</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>jooni0206@naver.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0507-1401-5015</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 수영강변대로 382 상가동 201호</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailpierna?igsh=MWR2ajNyeWhmc2M2eg==</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>27</v>
+      </c>
+      <c r="R209" t="n">
+        <v>114</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>1255340807</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1255340807</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>썬네일</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>sunnail3024@naver.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티2로 33 104동 241호 제니스상가 2층</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/sun_nail_zenith</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>23</v>
+      </c>
+      <c r="R210" t="n">
+        <v>28</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>1530024895</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1530024895</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>졔쌀롱</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>qhdwkzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>0507-1309-6714</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로 95 센텀대림아파트상가 B동 304호</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jye_salon</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>7</v>
+      </c>
+      <c r="R211" t="n">
+        <v>104</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>1894033440</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1894033440</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>네일미쁘다</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>lifeofbliss@naver.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>0507-1330-9883</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동129호</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mibbeuda?igsh=dWs1eXg5aGVhNnRs&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>5</v>
+      </c>
+      <c r="R212" t="n">
+        <v>57</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>1450226314</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1450226314</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>오드리 네일</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ardusy@naver.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>0507-1474-4547</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 양운로42번길 11</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>30</v>
+      </c>
+      <c r="R213" t="n">
+        <v>37</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>122450520</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/122450520</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>모드에 네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>bluetipe@naver.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0507-1410-3833</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀동로 90 220호</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modue_nail</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>24</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>1955791993</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1955791993</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>애플네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>coolmin0721@naver.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀중앙로 145 상가 2동 119호 (재송동,더샵센텀파크1차아파트)</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>1265414769</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265414769</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>네일은</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>sungunara226@naver.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0507-1470-3350</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로469번길 181 센텀마티안상가 1층 네일은</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_eun_nail</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>29</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>2067378490</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067378490</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>위니네일</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>dewdew2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>0507-1479-5242</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 790 해운대대림아크로텔 2층 203호</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weeny_nail/</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>41</v>
+      </c>
+      <c r="R217" t="n">
+        <v>211</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>1034464661</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034464661</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>공주네일</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>snow1blossom@naver.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 삼어로 55 주상가 104호</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gongju._.nail</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>2</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>1880647674</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1880647674</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>살롱드빠꼼</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>sooin9292@naver.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>0507-1437-8932</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 802 b동 202호 2층</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ppakkom_hana</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>7</v>
+      </c>
+      <c r="R219" t="n">
+        <v>12</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>13566496</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13566496</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>네일카운티 센텀점</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>nailcounty@naver.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0507-1402-2178</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀동로 25 센텀월드마크 1층 상가 B동 102호</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nailcounty_ct</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>295</v>
+      </c>
+      <c r="R220" t="n">
+        <v>691</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>37890465</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37890465</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>네일드메르</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>rpretty90@naver.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>0507-1433-0868</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 양운로42번길 18 에이원웨이 6층 601호</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__demer</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>24</v>
+      </c>
+      <c r="R221" t="n">
+        <v>500</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>1118215617</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1118215617</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>네일시오</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>jiali1998@naver.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 우동2로 61</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>10</v>
+      </c>
+      <c r="R222" t="n">
+        <v>24</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>1587651707</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587651707</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>글리츠네일 해운대점</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>glitz__@naver.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0507-1336-5456</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 구남로 21 상가 2층 217호</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/glitz__</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>50</v>
+      </c>
+      <c r="R223" t="n">
+        <v>180</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>1111062804</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111062804</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>로웰네일</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>hjhj8889@naver.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0507-1371-9974</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티2로 33 제니스 스퀘어 232호</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_lowell_nail</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>5</v>
+      </c>
+      <c r="R224" t="n">
+        <v>29</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>1828661616</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1828661616</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>임뷰네일</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>mneilacademy@naver.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0507-1386-3520</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티3로 46 지하1층 108-1호</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imbue_nail?igsh=MTlrOG9ldHAxZ3Jqcg==</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>131</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>1059402150</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1059402150</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>벨라네일</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>00bbangbbang00@naver.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 좌동순환로 473</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>1417246865</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1417246865</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>코지네일</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>syjang128@naver.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0507-1300-4419</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 64 화목데파트 상가 3층305호</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/cozy.nail__</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>28</v>
+      </c>
+      <c r="R227" t="n">
+        <v>92</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>1669238361</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1669238361</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>달자네일</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>lovemoon95@naver.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0507-1393-4787</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 대천로 187 제상가동 2층 225호</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dalja.nail</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>13</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>1628470007</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628470007</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>뷰티에홀리다 해운대점</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>chl4550@naver.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0507-1321-1286</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로27번길 11 대승코아 203호</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>http://instagram.com/beautyholida_nail2</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>746</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>63</v>
+      </c>
+      <c r="R229" t="n">
+        <v>809</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>1045058902</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045058902</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>오늘의뷰티</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>jayhan2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>051-743-7271</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 620 2층 227호</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Zxatpb</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>6</v>
+      </c>
+      <c r="R230" t="n">
+        <v>346</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>1518251845</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1518251845</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>네일, 쁨</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ljgda0118@naver.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 대천로 187 화목타운 상가 2층 237호</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail___.pp</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>4</v>
+      </c>
+      <c r="R231" t="n">
+        <v>146</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>1442010518</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1442010518</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>원뷰티</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>yoojuzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>0507-1389-8372</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로61번길 73 상가 B103호 원뷰티</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yoojuzz</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>14</v>
+      </c>
+      <c r="R232" t="n">
+        <v>21</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>1913663371</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1913663371</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>엔피케어 해운대점</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>np_care@naver.com</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>0507-1320-8125</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀남대로 50 3층 NP케어 부산센텀점</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://youtube.com/freshfoot_</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>64</v>
+      </c>
+      <c r="R233" t="n">
+        <v>279</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>1979973541</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1979973541</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>쥬디네일</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>sim_princess@naver.com</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 선수촌로 122 더스포츠센터동 1층 테라스방향 노란색가게</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://쥬디네일.com/</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>459</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>2</v>
+      </c>
+      <c r="R234" t="n">
+        <v>461</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>1968735765</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1968735765</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>퀸 네일</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>miinijk@naver.com</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>051-746-4144</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대해변로 117 대우마리나1차아파트상가동108호</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>5</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>1004464332</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004464332</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>네일에반하다</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>jjhrlove@naver.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0507-1311-8208</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 126 상가동108호 좌동 건영2차아파트</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>http://instagram.com/jin8208</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>2</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>1710359631</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710359631</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>연지네일</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>051-747-7519</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 센텀중앙로 145 더샵센텀파크1 상가6동 108호</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>4</v>
+      </c>
+      <c r="R237" t="n">
+        <v>9</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>19582081</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19582081</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>온네일</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 대천로 78</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>0</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>1955667882</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1955667882</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Ds공간디자인</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ddr1895@naver.com</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0507-1442-4435</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 달맞이길117번나길 15-15 대운가득빌딩205호</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://dsspace.co.kr</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>5</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>1593587399</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593587399</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
